--- a/excel-files/MANDALUYONG/ADDITION HILLS INTEGRATED SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/ADDITION HILLS INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="517" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FB402E-A5E4-4C0D-877B-A59EC0B556DF}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5559FF8-BC47-47B6-A507-C08E13F656F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -773,18 +773,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -797,6 +785,18 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5765,8 +5765,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5785,7 +5785,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="8.85546875" customWidth="1"/>
@@ -5818,38 +5818,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -6019,7 +6019,7 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="43" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1">
@@ -6090,7 +6090,7 @@
       <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="43" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1">
@@ -6161,7 +6161,7 @@
       <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="43" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1">
@@ -6232,7 +6232,7 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="43" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1">
@@ -6303,7 +6303,7 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="1">
@@ -6374,7 +6374,7 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="1">
@@ -6445,7 +6445,7 @@
       <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="1">
@@ -6516,7 +6516,7 @@
       <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="44" t="s">
         <v>64</v>
       </c>
       <c r="C12" s="1">
@@ -6584,7 +6584,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B13" s="49"/>
+      <c r="B13" s="45"/>
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6601,7 +6601,7 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="43" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1">
@@ -6672,7 +6672,7 @@
       <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="43" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="1">
@@ -6743,7 +6743,7 @@
       <c r="A16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="43" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="1">
@@ -6820,7 +6820,7 @@
       <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="43" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="1">
@@ -6897,7 +6897,7 @@
       <c r="A18" s="1">
         <v>2</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="1">
@@ -6974,7 +6974,7 @@
       <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="1">
@@ -7051,7 +7051,7 @@
       <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="1">
@@ -7128,7 +7128,7 @@
       <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="44" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="1">
@@ -7196,7 +7196,7 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B22" s="49"/>
+      <c r="B22" s="45"/>
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -7214,7 +7214,7 @@
       <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="43" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1">
@@ -7285,7 +7285,7 @@
       <c r="A24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="43" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="1">
@@ -7356,7 +7356,7 @@
       <c r="A25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="43" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="1">
@@ -7433,7 +7433,7 @@
       <c r="A26" s="1">
         <v>3</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="43" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="1">
@@ -7510,7 +7510,7 @@
       <c r="A27" s="1">
         <v>3</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="43" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="1">
@@ -7587,7 +7587,7 @@
       <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C28" s="1">
@@ -7664,7 +7664,7 @@
       <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="1">
@@ -7741,7 +7741,7 @@
       <c r="A30" s="1">
         <v>3</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="1">
@@ -7818,7 +7818,7 @@
       <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="44" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="1">
@@ -7886,7 +7886,7 @@
       </c>
     </row>
     <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B32" s="49"/>
+      <c r="B32" s="45"/>
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7904,7 +7904,7 @@
       <c r="A33" s="1">
         <v>4</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="1">
@@ -7975,7 +7975,7 @@
       <c r="A34" s="1">
         <v>4</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="1">
@@ -8046,7 +8046,7 @@
       <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C35" s="1">
@@ -8117,7 +8117,7 @@
       <c r="A36" s="1">
         <v>4</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="44" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="1">
@@ -8188,7 +8188,7 @@
       <c r="A37" s="1">
         <v>4</v>
       </c>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="44" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="1">
@@ -8259,7 +8259,7 @@
       <c r="A38" s="1">
         <v>4</v>
       </c>
-      <c r="B38" s="48" t="s">
+      <c r="B38" s="44" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="1">
@@ -8330,7 +8330,7 @@
       <c r="A39" s="1">
         <v>4</v>
       </c>
-      <c r="B39" s="48" t="s">
+      <c r="B39" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C39" s="1">
@@ -8401,7 +8401,7 @@
       <c r="A40" s="1">
         <v>4</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="44" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="1">
@@ -8472,7 +8472,7 @@
       <c r="A41" s="1">
         <v>4</v>
       </c>
-      <c r="B41" s="48" t="s">
+      <c r="B41" s="44" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="1">
@@ -8540,7 +8540,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B42" s="49"/>
+      <c r="B42" s="45"/>
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8558,7 +8558,7 @@
       <c r="A43" s="1">
         <v>5</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="1">
@@ -8639,7 +8639,7 @@
       <c r="A44" s="1">
         <v>5</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C44" s="1">
@@ -8716,7 +8716,7 @@
       <c r="A45" s="1">
         <v>5</v>
       </c>
-      <c r="B45" s="48" t="s">
+      <c r="B45" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="1">
@@ -8797,7 +8797,7 @@
       <c r="A46" s="1">
         <v>5</v>
       </c>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="44" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="1">
@@ -8874,7 +8874,7 @@
       <c r="A47" s="1">
         <v>5</v>
       </c>
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="44" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="1">
@@ -8951,7 +8951,7 @@
       <c r="A48" s="1">
         <v>5</v>
       </c>
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="44" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="1">
@@ -9028,7 +9028,7 @@
       <c r="A49" s="1">
         <v>5</v>
       </c>
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1">
@@ -9105,7 +9105,7 @@
       <c r="A50" s="1">
         <v>5</v>
       </c>
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="44" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="1">
@@ -9182,7 +9182,7 @@
       <c r="A51" s="1">
         <v>5</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="44" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="1">
@@ -9256,7 +9256,7 @@
       </c>
     </row>
     <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B52" s="49"/>
+      <c r="B52" s="45"/>
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -9274,7 +9274,7 @@
       <c r="A53" s="1">
         <v>6</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="1">
@@ -9345,7 +9345,7 @@
       <c r="A54" s="1">
         <v>6</v>
       </c>
-      <c r="B54" s="48" t="s">
+      <c r="B54" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C54" s="1">
@@ -9416,7 +9416,7 @@
       <c r="A55" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="1">
@@ -9487,7 +9487,7 @@
       <c r="A56" s="1">
         <v>6</v>
       </c>
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="44" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="1">
@@ -9558,7 +9558,7 @@
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="44" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="1">
@@ -9629,7 +9629,7 @@
       <c r="A58" s="1">
         <v>6</v>
       </c>
-      <c r="B58" s="48" t="s">
+      <c r="B58" s="44" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="1">
@@ -9700,7 +9700,7 @@
       <c r="A59" s="1">
         <v>6</v>
       </c>
-      <c r="B59" s="48" t="s">
+      <c r="B59" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="1">
@@ -9771,7 +9771,7 @@
       <c r="A60" s="1">
         <v>6</v>
       </c>
-      <c r="B60" s="48" t="s">
+      <c r="B60" s="44" t="s">
         <v>20</v>
       </c>
       <c r="C60" s="1">
@@ -9842,7 +9842,7 @@
       <c r="A61" s="1">
         <v>6</v>
       </c>
-      <c r="B61" s="48" t="s">
+      <c r="B61" s="44" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="1">
@@ -9910,7 +9910,7 @@
       </c>
     </row>
     <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B62" s="49"/>
+      <c r="B62" s="45"/>
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9928,7 +9928,7 @@
       <c r="A63" s="10">
         <v>7</v>
       </c>
-      <c r="B63" s="50" t="s">
+      <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="10">
@@ -9999,7 +9999,7 @@
       <c r="A64" s="10">
         <v>7</v>
       </c>
-      <c r="B64" s="50" t="s">
+      <c r="B64" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C64" s="10">
@@ -10070,7 +10070,7 @@
       <c r="A65" s="10">
         <v>7</v>
       </c>
-      <c r="B65" s="50" t="s">
+      <c r="B65" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="10">
@@ -10141,7 +10141,7 @@
       <c r="A66" s="10">
         <v>7</v>
       </c>
-      <c r="B66" s="50" t="s">
+      <c r="B66" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C66" s="10">
@@ -10212,7 +10212,7 @@
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="50" t="s">
+      <c r="B67" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C67" s="10">
@@ -10283,7 +10283,7 @@
       <c r="A68" s="10">
         <v>7</v>
       </c>
-      <c r="B68" s="50" t="s">
+      <c r="B68" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C68" s="10">
@@ -10354,7 +10354,7 @@
       <c r="A69" s="10">
         <v>7</v>
       </c>
-      <c r="B69" s="50" t="s">
+      <c r="B69" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C69" s="10">
@@ -10425,7 +10425,7 @@
       <c r="A70" s="10">
         <v>7</v>
       </c>
-      <c r="B70" s="50" t="s">
+      <c r="B70" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="10">
@@ -10496,7 +10496,7 @@
       <c r="A71" s="10">
         <v>7</v>
       </c>
-      <c r="B71" s="50" t="s">
+      <c r="B71" s="46" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="10">
@@ -10564,7 +10564,7 @@
       </c>
     </row>
     <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B72" s="49"/>
+      <c r="B72" s="45"/>
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10582,7 +10582,7 @@
       <c r="A73" s="10">
         <v>8</v>
       </c>
-      <c r="B73" s="50" t="s">
+      <c r="B73" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="10">
@@ -10659,7 +10659,7 @@
       <c r="A74" s="10">
         <v>8</v>
       </c>
-      <c r="B74" s="50" t="s">
+      <c r="B74" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C74" s="10">
@@ -10736,7 +10736,7 @@
       <c r="A75" s="10">
         <v>8</v>
       </c>
-      <c r="B75" s="50" t="s">
+      <c r="B75" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="10">
@@ -10813,7 +10813,7 @@
       <c r="A76" s="10">
         <v>8</v>
       </c>
-      <c r="B76" s="50" t="s">
+      <c r="B76" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C76" s="10">
@@ -10890,7 +10890,7 @@
       <c r="A77" s="10">
         <v>8</v>
       </c>
-      <c r="B77" s="50" t="s">
+      <c r="B77" s="46" t="s">
         <v>25</v>
       </c>
       <c r="C77" s="10">
@@ -10967,7 +10967,7 @@
       <c r="A78" s="10">
         <v>8</v>
       </c>
-      <c r="B78" s="50" t="s">
+      <c r="B78" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="10">
@@ -11044,7 +11044,7 @@
       <c r="A79" s="10">
         <v>8</v>
       </c>
-      <c r="B79" s="50" t="s">
+      <c r="B79" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C79" s="10">
@@ -11121,7 +11121,7 @@
       <c r="A80" s="10">
         <v>8</v>
       </c>
-      <c r="B80" s="50" t="s">
+      <c r="B80" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C80" s="10">
@@ -11198,7 +11198,7 @@
       <c r="A81" s="10">
         <v>8</v>
       </c>
-      <c r="B81" s="50" t="s">
+      <c r="B81" s="46" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="10">
@@ -11272,7 +11272,7 @@
       </c>
     </row>
     <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B82" s="49"/>
+      <c r="B82" s="45"/>
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -11290,7 +11290,7 @@
       <c r="A83" s="10">
         <v>9</v>
       </c>
-      <c r="B83" s="50" t="s">
+      <c r="B83" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="10">
@@ -11361,7 +11361,7 @@
       <c r="A84" s="10">
         <v>9</v>
       </c>
-      <c r="B84" s="50" t="s">
+      <c r="B84" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C84" s="10">
@@ -11432,7 +11432,7 @@
       <c r="A85" s="10">
         <v>9</v>
       </c>
-      <c r="B85" s="50" t="s">
+      <c r="B85" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C85" s="10">
@@ -11503,7 +11503,7 @@
       <c r="A86" s="10">
         <v>9</v>
       </c>
-      <c r="B86" s="50" t="s">
+      <c r="B86" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C86" s="10">
@@ -11574,7 +11574,7 @@
       <c r="A87" s="10">
         <v>9</v>
       </c>
-      <c r="B87" s="50" t="s">
+      <c r="B87" s="46" t="s">
         <v>25</v>
       </c>
       <c r="C87" s="10">
@@ -11645,7 +11645,7 @@
       <c r="A88" s="10">
         <v>9</v>
       </c>
-      <c r="B88" s="50" t="s">
+      <c r="B88" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C88" s="10">
@@ -11716,7 +11716,7 @@
       <c r="A89" s="10">
         <v>9</v>
       </c>
-      <c r="B89" s="50" t="s">
+      <c r="B89" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C89" s="10">
@@ -11787,7 +11787,7 @@
       <c r="A90" s="10">
         <v>9</v>
       </c>
-      <c r="B90" s="50" t="s">
+      <c r="B90" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C90" s="10">
@@ -11858,7 +11858,7 @@
       <c r="A91" s="10">
         <v>9</v>
       </c>
-      <c r="B91" s="50" t="s">
+      <c r="B91" s="46" t="s">
         <v>21</v>
       </c>
       <c r="C91" s="10">
@@ -11926,7 +11926,7 @@
       </c>
     </row>
     <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B92" s="49"/>
+      <c r="B92" s="45"/>
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11944,7 +11944,7 @@
       <c r="A93" s="10">
         <v>10</v>
       </c>
-      <c r="B93" s="50" t="s">
+      <c r="B93" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="10">
@@ -12015,7 +12015,7 @@
       <c r="A94" s="10">
         <v>10</v>
       </c>
-      <c r="B94" s="50" t="s">
+      <c r="B94" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C94" s="10">
@@ -12086,7 +12086,7 @@
       <c r="A95" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="50" t="s">
+      <c r="B95" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C95" s="10">
@@ -12157,7 +12157,7 @@
       <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="50" t="s">
+      <c r="B96" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C96" s="10">
@@ -12228,7 +12228,7 @@
       <c r="A97" s="10">
         <v>10</v>
       </c>
-      <c r="B97" s="50" t="s">
+      <c r="B97" s="46" t="s">
         <v>25</v>
       </c>
       <c r="C97" s="10">
@@ -12299,7 +12299,7 @@
       <c r="A98" s="10">
         <v>10</v>
       </c>
-      <c r="B98" s="50" t="s">
+      <c r="B98" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C98" s="10">
@@ -12370,7 +12370,7 @@
       <c r="A99" s="10">
         <v>10</v>
       </c>
-      <c r="B99" s="50" t="s">
+      <c r="B99" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C99" s="10">
@@ -12441,7 +12441,7 @@
       <c r="A100" s="10">
         <v>10</v>
       </c>
-      <c r="B100" s="50" t="s">
+      <c r="B100" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C100" s="10">
@@ -12512,7 +12512,7 @@
       <c r="A101" s="10">
         <v>10</v>
       </c>
-      <c r="B101" s="50" t="s">
+      <c r="B101" s="46" t="s">
         <v>21</v>
       </c>
       <c r="C101" s="10">
@@ -12580,7 +12580,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
-      <c r="B102" s="49"/>
+      <c r="B102" s="45"/>
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12598,7 +12598,7 @@
       <c r="A103" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B103" s="48" t="s">
+      <c r="B103" s="44" t="s">
         <v>27</v>
       </c>
       <c r="C103" s="1"/>
@@ -12667,7 +12667,7 @@
       <c r="A104" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B104" s="48" t="s">
+      <c r="B104" s="44" t="s">
         <v>28</v>
       </c>
       <c r="C104" s="1"/>
@@ -12736,7 +12736,7 @@
       <c r="A105" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B105" s="48" t="s">
+      <c r="B105" s="44" t="s">
         <v>29</v>
       </c>
       <c r="C105" s="1"/>
@@ -12805,7 +12805,7 @@
       <c r="A106" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B106" s="48" t="s">
+      <c r="B106" s="44" t="s">
         <v>30</v>
       </c>
       <c r="C106" s="1"/>
@@ -12874,7 +12874,7 @@
       <c r="A107" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B107" s="48" t="s">
+      <c r="B107" s="44" t="s">
         <v>31</v>
       </c>
       <c r="C107" s="1"/>
@@ -12943,7 +12943,7 @@
       <c r="A108" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B108" s="48" t="s">
+      <c r="B108" s="44" t="s">
         <v>32</v>
       </c>
       <c r="C108" s="1"/>
@@ -13012,7 +13012,7 @@
       <c r="A109" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B109" s="48" t="s">
+      <c r="B109" s="44" t="s">
         <v>33</v>
       </c>
       <c r="C109" s="1"/>
@@ -13081,7 +13081,7 @@
       <c r="A110" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B110" s="48" t="s">
+      <c r="B110" s="44" t="s">
         <v>34</v>
       </c>
       <c r="C110" s="1"/>
@@ -14144,186 +14144,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -14354,8 +14174,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 G14:G21 G33:G41 G23:G31 G53:G61 G63:G71 G43:G51 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14410,39 +14230,39 @@
   <sheetData>
     <row r="1" spans="1:28" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="43" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="44" t="s">
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="45" t="s">
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
     </row>
     <row r="2" spans="1:28" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -22050,7 +21870,7 @@
       <c r="A116" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B116" s="46" t="s">
+      <c r="B116" s="42" t="s">
         <v>28</v>
       </c>
       <c r="C116" s="1"/>
@@ -22122,7 +21942,7 @@
       <c r="A117" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B117" s="46" t="s">
+      <c r="B117" s="42" t="s">
         <v>29</v>
       </c>
       <c r="C117" s="1"/>
@@ -22266,7 +22086,7 @@
       <c r="A119" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B119" s="46" t="s">
+      <c r="B119" s="42" t="s">
         <v>31</v>
       </c>
       <c r="C119" s="1"/>
@@ -22482,7 +22302,7 @@
       <c r="A122" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B122" s="46" t="s">
+      <c r="B122" s="42" t="s">
         <v>34</v>
       </c>
       <c r="C122" s="1"/>
@@ -23078,186 +22898,36 @@
       <c r="AB140" s="7"/>
       <c r="AC140" s="7"/>
     </row>
-    <row r="141" spans="1:29">
-      <c r="K141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:29">
-      <c r="K142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:29">
-      <c r="K143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:29">
-      <c r="K144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="11:11">
-      <c r="K145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="11:11">
-      <c r="K146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="11:11">
-      <c r="K147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="11:11">
-      <c r="K148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="11:11">
-      <c r="K149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="11:11">
-      <c r="K150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="11:11">
-      <c r="K151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="11:11">
-      <c r="K152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="11:11">
-      <c r="K153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="11:11">
-      <c r="K154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="11:11">
-      <c r="K155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="11:11">
-      <c r="K156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="11:11">
-      <c r="K157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="11:11">
-      <c r="K158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="11:11">
-      <c r="K159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="11:11">
-      <c r="K160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="11:11">
-      <c r="K161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="11:11">
-      <c r="K162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="11:11">
-      <c r="K163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="11:11">
-      <c r="K164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="11:11">
-      <c r="K165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="11:11">
-      <c r="K166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="11:11">
-      <c r="K167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="11:11">
-      <c r="K168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="11:11">
-      <c r="K169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="11:11">
-      <c r="K170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="141" spans="1:29"/>
+    <row r="142" spans="1:29"/>
+    <row r="143" spans="1:29"/>
+    <row r="144" spans="1:29"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2 C115:C122" name="Textbooks"/>
@@ -23282,12 +22952,15 @@
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="W1:AB1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T115:T122 Z115:Z122 H115:H122 Z3:Z10 T3:T10 N3:N10 H3:H10 H12:H19 Z12:Z19 T12:T19 N12:N19 N21:N29 H21:H29 Z21:Z29 T21:T29 T31:T41 N31:N41 H31:H41 Z31:Z41 Z43:Z53 T43:T53 N43:N53 H43:H53 H55:H65 Z55:Z65 N115:N122 N55:N65 N67:N77 H67:H77 Z67:Z77 T67:T77 T79:T89 N79:N89 H79:H89 Z79:Z89 Z91:Z101 T91:T101 N91:N101 H91:H101 H103:H113 Z103:Z113 T103:T113 N103:N113 T55:T65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y21:Y29 Y31:Y41 Y43:Y53 Y67:Y77 Y79:Y89 Y55:Y65 Y91:Y101 Y103:Y113 Y12:Y19 Y3:Y10 M21:M29 M31:M41 M43:M53 M67:M77 M79:M89 M55:M65 M91:M101 M103:M113 M12:M19 M3:M10 S21:S29 S31:S41 S43:S53 S67:S77 S79:S89 F103:G113 S91:S101 S103:S113 S12:S19 S3:S10 F21:G29 F31:G41 F43:G53 F67:G77 F79:G89 F55:G65 F3:G10 F91:G101 Y115:Y122 F12:G19 F115:G122 S115:S122 M115:M122 S55:S65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21:G29 G43:G53 G115:G122 G3:G10 G91:G101 G55:G65 G79:G89 G31:G41 G103:G113 G12:G19 G67:G77" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 M115:M122 M103:M113 M91:M101 M79:M89 M67:M77 M55:M65 M43:M53 M31:M41 M21:M29 M12:M19 M3:M10 S115:S122 S103:S113 S91:S101 S79:S89 S67:S77 S55:S65 S43:S53 S31:S41 S21:S29 S12:S19 S3:S10 Y115:Y122 Y103:Y113 Y91:Y101 Y79:Y89 Y67:Y77 Y55:Y65 Y43:Y53 Y31:Y41 Y21:Y29 Y12:Y19 Y3:Y10" xr:uid="{6AD79357-351B-4CD2-90EC-34339AE4C64D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
